--- a/downloads/Th1_pre_post+2h_results.xlsx
+++ b/downloads/Th1_pre_post+2h_results.xlsx
@@ -764,7 +764,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pre/post designs only</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C4">
@@ -875,7 +875,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pre/post designs only</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C7">
@@ -986,7 +986,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pre/post designs only</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C10">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pre/post designs only</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C13">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pre/post designs only</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C16">

--- a/downloads/Th1_pre_post+2h_results.xlsx
+++ b/downloads/Th1_pre_post+2h_results.xlsx
@@ -624,7 +624,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -683,6 +683,46 @@
           <t>pi_upper</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>eg_t</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>eg_df</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>eg_p</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>tf_k0</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>tf_side</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>tf_g</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>tf_lo</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>tf_up</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -720,6 +760,23 @@
       <c r="K2">
         <v>0.7594019825207616</v>
       </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="Q2">
+        <v>-0.4257066012857283</v>
+      </c>
+      <c r="R2">
+        <v>-0.9082252429140272</v>
+      </c>
+      <c r="S2">
+        <v>0.05681204034257059</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -757,6 +814,23 @@
       <c r="K3">
         <v>0.1464972113907543</v>
       </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q3">
+        <v>-0.6430608576778517</v>
+      </c>
+      <c r="R3">
+        <v>-1.105602004208741</v>
+      </c>
+      <c r="S3">
+        <v>-0.1805197111469628</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -831,6 +905,23 @@
       <c r="K5">
         <v>0.7289784528126326</v>
       </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="Q5">
+        <v>-0.4209779906990635</v>
+      </c>
+      <c r="R5">
+        <v>-0.8774333802958822</v>
+      </c>
+      <c r="S5">
+        <v>0.0354773988977552</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -868,6 +959,23 @@
       <c r="K6">
         <v>0.09784866991276764</v>
       </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q6">
+        <v>-0.5447479494630081</v>
+      </c>
+      <c r="R6">
+        <v>-0.9983734247896632</v>
+      </c>
+      <c r="S6">
+        <v>-0.09112247413635305</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -942,6 +1050,23 @@
       <c r="K8">
         <v>0.6917308699592857</v>
       </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="Q8">
+        <v>-0.4136577294133379</v>
+      </c>
+      <c r="R8">
+        <v>-0.8408937952897492</v>
+      </c>
+      <c r="S8">
+        <v>0.01357833646307338</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -979,6 +1104,23 @@
       <c r="K9">
         <v>0.04780266587514592</v>
       </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q9">
+        <v>-0.5333263190335595</v>
+      </c>
+      <c r="R9">
+        <v>-0.943560210804397</v>
+      </c>
+      <c r="S9">
+        <v>-0.1230924272627221</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -1053,6 +1195,23 @@
       <c r="K11">
         <v>0.6479236902216795</v>
       </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="Q11">
+        <v>-0.402768020702893</v>
+      </c>
+      <c r="R11">
+        <v>-0.797135420942197</v>
+      </c>
+      <c r="S11">
+        <v>-0.008400620463589026</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -1090,6 +1249,23 @@
       <c r="K12">
         <v>-0.003351473438365726</v>
       </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q12">
+        <v>-0.517250041005906</v>
+      </c>
+      <c r="R12">
+        <v>-0.8800242526240205</v>
+      </c>
+      <c r="S12">
+        <v>-0.1544758293877915</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -1164,6 +1340,23 @@
       <c r="K14">
         <v>0.5989784999688186</v>
       </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="Q14">
+        <v>-0.3867253455548639</v>
+      </c>
+      <c r="R14">
+        <v>-0.7440573566818836</v>
+      </c>
+      <c r="S14">
+        <v>-0.02939333442784436</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -1200,6 +1393,23 @@
       </c>
       <c r="K15">
         <v>0.02699461952646182</v>
+      </c>
+      <c r="O15">
+        <v>2</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q15">
+        <v>-0.66820274507734</v>
+      </c>
+      <c r="R15">
+        <v>-1.074790996297532</v>
+      </c>
+      <c r="S15">
+        <v>-0.2616144938571481</v>
       </c>
     </row>
     <row r="16">
